--- a/sheets/tickets.xlsx
+++ b/sheets/tickets.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="15324" windowHeight="6948" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tickets" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="tickets" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -26,7 +25,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -54,7 +55,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -417,15 +418,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="1" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,6 +456,358 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>167dc44f-1e7a-4a75-8fa4-c31d35ef20fe</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>T-MOCK-20261019154945-0001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ole5.test@example.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>OLE5</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Error creating new outgoing transaction</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-10-19T12:49:45+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2d5bf04b-ae92-458c-a0a4-a44b48dba40b</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>T-MOCK-20261020094235-0001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ole5.test@example.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>OLE5</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>All users unable to sign in</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-10-20T06:42:35+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cfecd095-30e7-4f16-8e1d-f148650901bb</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>T-MOCK-20261020094441-0002</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ole5.test@example.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>OLE5</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Mobile app crashes when opening Inbox</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-20T06:44:41+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>dc1c7d43-e915-4307-b813-70d3b0e9e4cc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>T-MOCK-20261020094534-0003</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ole5.test@example.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>OLE5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>All users unable to sign in</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-20T06:45:34+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>95d3d63b-5b77-4fb6-aade-6aac5084b6c2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>T-MOCK-20261020103942-0001</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ole5.test@example.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>OLE5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Create correspondence screen not working</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-20T07:39:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>19884e2f-b34f-4c1b-8e03-0a46654563e4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>T-MOCK-20261020115633-0001</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ole5.test@example.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>OLE5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Password reset email not received</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-20T08:56:33+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>8de54eb6-c8f0-46bb-a994-47734b06b5f3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>T-MOCK-20261020151240-0001</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ole5.test@example.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>OLE5</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>System not opening (all pages)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-20T12:12:40+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>e8595164-9f24-4cfd-b4b8-d25f9eed109b</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>T-MOCK-20261020155029-0001</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ole5.test@example.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>OLE5</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>System not opening (complete outage)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-20T12:50:29+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>e8888448-b506-4e86-8e5d-9f0cd6ad1124</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>T-MOCK-20261020163353-0001</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ole5.test@example.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OLE5</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>System does not open</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-20T13:33:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>bcec29e7-5f53-4585-871b-fd4023a97856</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T-MOCK-20261021111735-0001</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ole5.test@example.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>OLE5</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>System not opening for any user</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-21T08:17:35+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6611a741-5dbe-4126-bef7-2db9722da6e1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>T-MOCK-20261021141333-0001</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ole5.test@example.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>OLE5</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Night mode availability question</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-21T11:13:33+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
